--- a/project-debutade-kasboek/static/category_test_set.xlsx
+++ b/project-debutade-kasboek/static/category_test_set.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project-debutade-kasboek\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Debutade\project-debutade-kasboek\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{565D71F2-76DF-480C-AA56-C624E86BD047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6E75CB-69F7-4B8B-84CB-84DF3028BD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6708" yWindow="3060" windowWidth="20844" windowHeight="12420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Kas!$A$1:$D$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Kas!$A$1:$D$146</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,9 +56,6 @@
     <t>Bij</t>
   </si>
   <si>
-    <t>8700;Opbrengst koffie</t>
-  </si>
-  <si>
     <t>Af</t>
   </si>
   <si>
@@ -378,6 +375,9 @@
   </si>
   <si>
     <t>Begin saldo 2025</t>
+  </si>
+  <si>
+    <t>8700;Koffie</t>
   </si>
 </sst>
 </file>
@@ -842,21 +842,21 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>285</v>
       </c>
       <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -867,10 +867,10 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -881,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -895,10 +895,10 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -909,10 +909,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -923,10 +923,10 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -940,7 +940,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -954,7 +954,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -968,7 +968,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -979,10 +979,10 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
         <v>13</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -993,66 +993,66 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
         <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14">
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15">
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B16">
         <v>21.35</v>
       </c>
       <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
         <v>19</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B17">
         <v>7.96</v>
       </c>
       <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
         <v>21</v>
-      </c>
-      <c r="D17" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1063,10 +1063,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1077,10 +1077,10 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1091,10 +1091,10 @@
         <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1105,10 +1105,10 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1119,10 +1119,10 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1133,24 +1133,24 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24">
         <v>118.1</v>
       </c>
       <c r="C24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" t="s">
         <v>28</v>
-      </c>
-      <c r="D24" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1161,24 +1161,24 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26">
         <v>375</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1189,10 +1189,10 @@
         <v>250</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1203,10 +1203,10 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1217,10 +1217,10 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D29" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1231,10 +1231,10 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1245,10 +1245,10 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1259,10 +1259,10 @@
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1273,10 +1273,10 @@
         <v>343</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1287,10 +1287,10 @@
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1301,10 +1301,10 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D35" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1315,10 +1315,10 @@
         <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1329,10 +1329,10 @@
         <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1343,10 +1343,10 @@
         <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D38" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1357,10 +1357,10 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D39" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1371,10 +1371,10 @@
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D40" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1385,66 +1385,66 @@
         <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D41" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B42">
         <v>15</v>
       </c>
       <c r="C42" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
         <v>40</v>
-      </c>
-      <c r="D42" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B43">
         <v>180</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B44">
         <v>135</v>
       </c>
       <c r="C44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B45">
         <v>65.25</v>
       </c>
       <c r="C45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1455,10 +1455,10 @@
         <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D46" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1469,10 +1469,10 @@
         <v>20</v>
       </c>
       <c r="C47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D47" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1483,10 +1483,10 @@
         <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D48" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1497,10 +1497,10 @@
         <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1511,10 +1511,10 @@
         <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1525,10 +1525,10 @@
         <v>210</v>
       </c>
       <c r="C51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1539,10 +1539,10 @@
         <v>30</v>
       </c>
       <c r="C52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1553,10 +1553,10 @@
         <v>30</v>
       </c>
       <c r="C53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D53" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1567,10 +1567,10 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D54" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1581,10 +1581,10 @@
         <v>20</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D55" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1595,10 +1595,10 @@
         <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1609,10 +1609,10 @@
         <v>30</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D57" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1623,10 +1623,10 @@
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D58" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1637,10 +1637,10 @@
         <v>10</v>
       </c>
       <c r="C59" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D59" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1651,10 +1651,10 @@
         <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D60" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1665,10 +1665,10 @@
         <v>20</v>
       </c>
       <c r="C61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D61" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1679,10 +1679,10 @@
         <v>20</v>
       </c>
       <c r="C62" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D62" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1693,10 +1693,10 @@
         <v>20</v>
       </c>
       <c r="C63" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D63" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1707,10 +1707,10 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D64" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1721,24 +1721,24 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B66">
         <v>285</v>
       </c>
       <c r="C66" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1749,10 +1749,10 @@
         <v>20</v>
       </c>
       <c r="C67" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D67" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1763,10 +1763,10 @@
         <v>30</v>
       </c>
       <c r="C68" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D68" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1777,10 +1777,10 @@
         <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D69" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1791,10 +1791,10 @@
         <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D70" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1805,10 +1805,10 @@
         <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D71" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1819,10 +1819,10 @@
         <v>50</v>
       </c>
       <c r="C72" t="s">
+        <v>56</v>
+      </c>
+      <c r="D72" t="s">
         <v>57</v>
-      </c>
-      <c r="D72" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1833,10 +1833,10 @@
         <v>30</v>
       </c>
       <c r="C73" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D73" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1847,10 +1847,10 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D74" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1861,10 +1861,10 @@
         <v>20</v>
       </c>
       <c r="C75" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D75" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1875,10 +1875,10 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D76" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1889,10 +1889,10 @@
         <v>30</v>
       </c>
       <c r="C77" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D77" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1903,10 +1903,10 @@
         <v>5</v>
       </c>
       <c r="C78" t="s">
+        <v>63</v>
+      </c>
+      <c r="D78" t="s">
         <v>64</v>
-      </c>
-      <c r="D78" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1917,10 +1917,10 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D79" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1931,10 +1931,10 @@
         <v>30</v>
       </c>
       <c r="C80" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D80" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1945,10 +1945,10 @@
         <v>20</v>
       </c>
       <c r="C81" t="s">
-        <v>67</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>6</v>
+        <v>66</v>
+      </c>
+      <c r="D81" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1959,10 +1959,10 @@
         <v>20</v>
       </c>
       <c r="C82" t="s">
-        <v>67</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>6</v>
+        <v>66</v>
+      </c>
+      <c r="D82" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1973,66 +1973,66 @@
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>63</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>6</v>
+        <v>62</v>
+      </c>
+      <c r="D83" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B84">
         <v>15.9</v>
       </c>
       <c r="C84" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B85">
         <v>50</v>
       </c>
       <c r="C85" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B86">
         <v>50</v>
       </c>
       <c r="C86" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B87" s="3">
         <v>42.24</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2043,10 +2043,10 @@
         <v>10</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>6</v>
+        <v>72</v>
+      </c>
+      <c r="D88" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2057,38 +2057,38 @@
         <v>20</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>6</v>
+        <v>65</v>
+      </c>
+      <c r="D89" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B90" s="3">
         <v>50</v>
       </c>
       <c r="C90" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B91" s="3">
         <v>260</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2099,10 +2099,10 @@
         <v>250</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>6</v>
+        <v>76</v>
+      </c>
+      <c r="D92" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2113,10 +2113,10 @@
         <v>10</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>6</v>
+        <v>66</v>
+      </c>
+      <c r="D93" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -2127,10 +2127,10 @@
         <v>20</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>6</v>
+        <v>61</v>
+      </c>
+      <c r="D94" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -2141,10 +2141,10 @@
         <v>10</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>6</v>
+        <v>61</v>
+      </c>
+      <c r="D95" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2155,24 +2155,24 @@
         <v>10</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>6</v>
+        <v>61</v>
+      </c>
+      <c r="D96" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B97" s="3">
         <v>52.87</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2183,10 +2183,10 @@
         <v>10</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>6</v>
+        <v>78</v>
+      </c>
+      <c r="D98" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2197,10 +2197,10 @@
         <v>20</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>6</v>
+        <v>62</v>
+      </c>
+      <c r="D99" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2211,80 +2211,80 @@
         <v>29</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
+      </c>
+      <c r="D100" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B101" s="3">
         <v>16.62</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B102" s="3">
         <v>18.149999999999999</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B103" s="7">
         <v>21.31</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B104" s="7">
         <v>9.75</v>
       </c>
       <c r="C104" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B105" s="7">
         <v>12.54</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2295,10 +2295,10 @@
         <v>40</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2309,10 +2309,10 @@
         <v>80</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2323,10 +2323,10 @@
         <v>10</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>6</v>
+        <v>88</v>
+      </c>
+      <c r="D108" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2337,10 +2337,10 @@
         <v>20</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>6</v>
+        <v>89</v>
+      </c>
+      <c r="D109" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2351,66 +2351,66 @@
         <v>20</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>6</v>
+        <v>62</v>
+      </c>
+      <c r="D110" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B111" s="7">
         <v>190</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B112" s="7">
         <v>170</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B113" s="7">
         <v>40</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B114" s="7">
         <v>80</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2421,10 +2421,10 @@
         <v>20</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>6</v>
+        <v>66</v>
+      </c>
+      <c r="D115" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2435,10 +2435,10 @@
         <v>10</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
+      </c>
+      <c r="D116" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2449,10 +2449,10 @@
         <v>10</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>6</v>
+        <v>94</v>
+      </c>
+      <c r="D117" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2463,10 +2463,10 @@
         <v>10</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>6</v>
+        <v>61</v>
+      </c>
+      <c r="D118" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2477,10 +2477,10 @@
         <v>40</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>6</v>
+        <v>66</v>
+      </c>
+      <c r="D119" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2491,10 +2491,10 @@
         <v>10</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>6</v>
+        <v>88</v>
+      </c>
+      <c r="D120" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2505,24 +2505,24 @@
         <v>10</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>6</v>
+        <v>95</v>
+      </c>
+      <c r="D121" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B122" s="7">
         <v>4.99</v>
       </c>
       <c r="C122" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2533,10 +2533,10 @@
         <v>250</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>6</v>
+        <v>98</v>
+      </c>
+      <c r="D123" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2547,10 +2547,10 @@
         <v>70</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>6</v>
+        <v>99</v>
+      </c>
+      <c r="D124" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2561,10 +2561,10 @@
         <v>10</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>6</v>
+        <v>65</v>
+      </c>
+      <c r="D125" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2575,10 +2575,10 @@
         <v>10</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>6</v>
+        <v>62</v>
+      </c>
+      <c r="D126" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2589,10 +2589,10 @@
         <v>10</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>6</v>
+        <v>66</v>
+      </c>
+      <c r="D127" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2603,10 +2603,10 @@
         <v>30</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>6</v>
+        <v>66</v>
+      </c>
+      <c r="D128" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2617,10 +2617,10 @@
         <v>10</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>6</v>
+        <v>62</v>
+      </c>
+      <c r="D129" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2631,66 +2631,66 @@
         <v>10</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
+      </c>
+      <c r="D130" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B131" s="7">
         <v>180</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B132" s="7">
         <v>6.25</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B133" s="7">
         <v>2</v>
       </c>
       <c r="C133" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B134" s="7">
         <v>20.04</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2701,24 +2701,24 @@
         <v>40</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
+      </c>
+      <c r="D135" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B136" s="7">
         <v>7</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2729,80 +2729,80 @@
         <v>90</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
+      </c>
+      <c r="D137" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B138" s="7">
         <v>4.1500000000000004</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B139" s="7">
         <v>35.35</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B140" s="7">
         <v>7</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B141" s="7">
         <v>21.35</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B142" s="7">
         <v>14.3</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2813,10 +2813,10 @@
         <v>20</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
+      </c>
+      <c r="D143" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2827,10 +2827,10 @@
         <v>100</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
+      </c>
+      <c r="D144" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -2841,10 +2841,10 @@
         <v>40</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
+      </c>
+      <c r="D145" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
@@ -2855,7 +2855,7 @@
         <v>80.5</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2873,7 +2873,7 @@
       <c r="D156" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D115" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:D146" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0"/>
 </worksheet>
@@ -3075,15 +3075,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="44247548-1aeb-473a-964e-c253877890f7">
@@ -3092,6 +3083,15 @@
     <TaxCatchAll xmlns="f31906ca-9024-40e8-a341-00d1353de50a" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3114,14 +3114,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513DA33D-AE90-4AF8-AD62-FCFFBACAF26A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CD08D3E-D87C-4719-B5F8-AAB2A1AA2FC4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3130,4 +3122,12 @@
     <ds:schemaRef ds:uri="f31906ca-9024-40e8-a341-00d1353de50a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513DA33D-AE90-4AF8-AD62-FCFFBACAF26A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>